--- a/assets/colors.xlsx
+++ b/assets/colors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlanglois/IET Dropbox/Projets en cours/Projet avec NZA/Report/Figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlanglois/IET Dropbox/Projets en cours/à archiver ou reclasser/Projet avec NZA/Report/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10F4801-85D9-754F-AF0A-A847182F5870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5403DD0-5948-9E4C-BF20-11D496FCBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29560" yWindow="660" windowWidth="38240" windowHeight="20940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="liste référence" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="958">
   <si>
     <t>variable</t>
   </si>
@@ -2757,15 +2757,9 @@
     <t>23 juin, total</t>
   </si>
   <si>
-    <t>Bi-énergie bois et électrique; Existant</t>
-  </si>
-  <si>
     <t>Bois; Existant</t>
   </si>
   <si>
-    <t>Bi-énergie bois et mazout; Existant</t>
-  </si>
-  <si>
     <t>LE-LP</t>
   </si>
   <si>
@@ -2881,6 +2875,42 @@
   </si>
   <si>
     <t>HP with natural gas backup</t>
+  </si>
+  <si>
+    <t>Bi-énergie bois et électrique (système existant)</t>
+  </si>
+  <si>
+    <t>Bi-énergie bois et mazout (système existant)</t>
+  </si>
+  <si>
+    <t>Chaudière au mazout (système existant)</t>
+  </si>
+  <si>
+    <t>Chaudière au mazout (nouveau système)</t>
+  </si>
+  <si>
+    <t>Fournaise au gaz naturel (système existant)</t>
+  </si>
+  <si>
+    <t>Fournaise au gaz naturel (nouveau système)</t>
+  </si>
+  <si>
+    <t>Plinthes électriques (système existant)</t>
+  </si>
+  <si>
+    <t>Thermpompe à air (système existant)</t>
+  </si>
+  <si>
+    <t>Thermpompe avec plinthes comme appoint</t>
+  </si>
+  <si>
+    <t>Thermpompe avec chaudière au mazout comme appoint</t>
+  </si>
+  <si>
+    <t>Thermpompe avec système au bois comme appoint</t>
+  </si>
+  <si>
+    <t>Thermpompe avec gaz naturel comme appoint</t>
   </si>
 </sst>
 </file>
@@ -5777,13 +5807,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D92" s="17" t="s">
         <v>223</v>
@@ -5791,13 +5821,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D93" s="138" t="s">
         <v>603</v>
@@ -5945,13 +5975,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D104" s="21" t="s">
         <v>240</v>
@@ -5959,13 +5989,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D105" s="49" t="s">
         <v>474</v>
@@ -10073,13 +10103,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D399" s="49" t="s">
         <v>474</v>
@@ -10087,13 +10117,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>906</v>
+        <v>946</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D400" s="142" t="s">
         <v>632</v>
@@ -10101,13 +10131,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>908</v>
+        <v>947</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D401" s="80" t="s">
         <v>45</v>
@@ -10115,10 +10145,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>948</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D402" s="89" t="s">
         <v>139</v>
@@ -10126,10 +10159,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>949</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D403" s="45" t="s">
         <v>462</v>
@@ -10137,10 +10173,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>950</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D404" s="77" t="s">
         <v>38</v>
@@ -10148,10 +10187,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>951</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D405" s="151" t="s">
         <v>135</v>
@@ -10159,10 +10201,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>952</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D406" s="75" t="s">
         <v>29</v>
@@ -10170,10 +10215,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>953</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D407" s="80" t="s">
         <v>45</v>
@@ -10181,10 +10229,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>954</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D408" s="83" t="s">
         <v>56</v>
@@ -10192,10 +10243,13 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>955</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D409" s="82" t="s">
         <v>49</v>
@@ -10203,10 +10257,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>956</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D410" s="24" t="s">
         <v>305</v>
@@ -10214,10 +10271,13 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>957</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D411" s="92" t="s">
         <v>185</v>
@@ -10225,13 +10285,13 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D412" s="77" t="s">
         <v>38</v>
@@ -10239,13 +10299,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D413" s="82" t="s">
         <v>49</v>
@@ -10253,13 +10313,13 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D414" s="75" t="s">
         <v>29</v>
@@ -10267,13 +10327,13 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D415" s="83" t="s">
         <v>56</v>
@@ -10281,13 +10341,13 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D416" s="24" t="s">
         <v>305</v>
@@ -10295,13 +10355,13 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D417" s="77" t="s">
         <v>38</v>
@@ -10309,13 +10369,13 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D418" s="82" t="s">
         <v>49</v>
@@ -10323,13 +10383,13 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D419" s="75" t="s">
         <v>29</v>
@@ -10337,13 +10397,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D420" s="83" t="s">
         <v>56</v>
@@ -10351,13 +10411,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D421" s="24" t="s">
         <v>305</v>
@@ -10365,13 +10425,13 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B422" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="C422" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>925</v>
       </c>
       <c r="D422" s="82" t="s">
         <v>49</v>
@@ -10379,13 +10439,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B423" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="B423" s="1" t="s">
+      <c r="C423" s="1" t="s">
         <v>924</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="D423" s="80" t="s">
         <v>45</v>
